--- a/vshop_autotest/data/test_data.xlsx
+++ b/vshop_autotest/data/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_tqs\vshop_autotest\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E9A99D-0CE0-4145-9962-83A27AD4437F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3B44D6-00F3-4101-A013-6C311A308B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28650" yWindow="19050" windowWidth="16590" windowHeight="8865" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28710" yWindow="19110" windowWidth="16590" windowHeight="8865" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user_table" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="74">
   <si>
     <t>请求方式</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -205,34 +205,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"Authorization":"{{TOKEN}}"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新曾成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加一个用户成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"username": "tqs_test_add","password": "tqs_test_add"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>注册成功</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>修改用户状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>put</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -246,14 +222,6 @@
   </si>
   <si>
     <t>/api/auth/register</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/user/{user_id}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{'tqs_test_add':'$..id'}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -715,10 +683,10 @@
         <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -726,10 +694,10 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -748,10 +716,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -762,7 +730,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="29.625" bestFit="1" customWidth="1"/>
@@ -904,13 +872,13 @@
         <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
@@ -922,7 +890,7 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="3" t="b">
@@ -944,11 +912,9 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>44</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -963,80 +929,6 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1006,7 @@
     </row>
     <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>23</v>
@@ -1176,25 +1068,25 @@
         <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="R3" s="3" t="b">
         <v>1</v>
@@ -1217,10 +1109,10 @@
         <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>29</v>
@@ -1229,7 +1121,7 @@
         <v>18</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="R4" s="3" t="b">
         <v>1</v>
@@ -1243,25 +1135,25 @@
         <v>40</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="R5" s="3" t="b">
         <v>1</v>
@@ -1275,28 +1167,28 @@
         <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="J6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="R6" s="3" t="b">
         <v>1</v>
@@ -1310,25 +1202,25 @@
         <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="R7" s="3" t="b">
         <v>1</v>

--- a/vshop_autotest/data/test_data.xlsx
+++ b/vshop_autotest/data/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_tqs\vshop_autotest\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3B44D6-00F3-4101-A013-6C311A308B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9E00A6-9E4E-42E6-97DD-17540558E8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28710" yWindow="19110" windowWidth="16590" windowHeight="8865" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28410" yWindow="19110" windowWidth="16590" windowHeight="8865" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user_table" sheetId="3" r:id="rId1"/>
@@ -730,7 +730,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="29.625" bestFit="1" customWidth="1"/>
@@ -929,6 +929,36 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
